--- a/diseases/d021/2005-2009.xlsx
+++ b/diseases/d021/2005-2009.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -2197,9 +2191,6 @@
       <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.07624737851981726</v>
       </c>
@@ -2741,9 +2732,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -3333,9 +3321,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3877,9 +3862,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4469,9 +4451,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5013,9 +4992,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -5605,9 +5581,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -6149,9 +6122,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -6741,9 +6711,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -7285,9 +7252,6 @@
       <c r="O42" t="n">
         <v>4</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.008359169436268481</v>
       </c>
@@ -7877,9 +7841,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -8421,9 +8382,6 @@
       <c r="O49" t="n">
         <v>6</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.01253875415440272</v>
       </c>
@@ -9013,9 +8971,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -9557,9 +9512,6 @@
       <c r="O56" t="n">
         <v>7</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.01462854651346984</v>
       </c>
@@ -10149,9 +10101,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10693,9 +10642,6 @@
       <c r="O63" t="n">
         <v>6</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.01253875415440272</v>
       </c>
@@ -11285,9 +11231,6 @@
       <c r="O67" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -11829,9 +11772,6 @@
       <c r="O70" t="n">
         <v>5</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.0104489617953356</v>
       </c>
@@ -12421,9 +12361,6 @@
       <c r="O74" t="n">
         <v>3</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -12965,9 +12902,6 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -13557,9 +13491,6 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -14101,9 +14032,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -14693,9 +14621,6 @@
       <c r="O88" t="n">
         <v>3</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -15237,9 +15162,6 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -15829,9 +15751,6 @@
       <c r="O95" t="n">
         <v>3</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -16373,9 +16292,6 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -16965,9 +16881,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -17509,9 +17422,6 @@
       <c r="O105" t="n">
         <v>2</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -18101,9 +18011,6 @@
       <c r="O109" t="n">
         <v>3</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -18645,9 +18552,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -19237,9 +19141,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -19781,9 +19682,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -20373,9 +20271,6 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -20917,9 +20812,6 @@
       <c r="O126" t="n">
         <v>3</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -21509,9 +21401,6 @@
       <c r="O130" t="n">
         <v>3</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -22053,9 +21942,6 @@
       <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -22645,9 +22531,6 @@
       <c r="O137" t="n">
         <v>2</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -23189,9 +23072,6 @@
       <c r="O140" t="n">
         <v>8</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.01666440395306741</v>
       </c>
@@ -23781,9 +23661,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -24325,9 +24202,6 @@
       <c r="O147" t="n">
         <v>10</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.02083050494133427</v>
       </c>
@@ -24917,9 +24791,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -25461,9 +25332,6 @@
       <c r="O154" t="n">
         <v>3</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -26053,9 +25921,6 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -26597,9 +26462,6 @@
       <c r="O161" t="n">
         <v>3</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -27189,9 +27051,6 @@
       <c r="O165" t="n">
         <v>4</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -27733,9 +27592,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -28325,9 +28181,6 @@
       <c r="O172" t="n">
         <v>3</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -28869,9 +28722,6 @@
       <c r="O175" t="n">
         <v>2</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -29461,9 +29311,6 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -30005,9 +29852,6 @@
       <c r="O182" t="n">
         <v>5</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.010378155386039</v>
       </c>
@@ -30597,9 +30441,6 @@
       <c r="O186" t="n">
         <v>3</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -31141,9 +30982,6 @@
       <c r="O189" t="n">
         <v>2</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -31733,9 +31571,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -32277,9 +32112,6 @@
       <c r="O196" t="n">
         <v>10</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.02075631077207799</v>
       </c>
@@ -32869,9 +32701,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -33413,9 +33242,6 @@
       <c r="O203" t="n">
         <v>5</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.010378155386039</v>
       </c>
@@ -34005,9 +33831,6 @@
       <c r="O207" t="n">
         <v>3</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -34549,9 +34372,6 @@
       <c r="O210" t="n">
         <v>7</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.0145294175404546</v>
       </c>
@@ -35141,9 +34961,6 @@
       <c r="O214" t="n">
         <v>5</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.09454101283677872</v>
       </c>
@@ -35685,9 +35502,6 @@
       <c r="O217" t="n">
         <v>18</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.03736135938974038</v>
       </c>
@@ -36277,9 +36091,6 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -36821,9 +36632,6 @@
       <c r="O224" t="n">
         <v>14</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.02905883508090919</v>
       </c>
@@ -37413,9 +37221,6 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -37957,9 +37762,6 @@
       <c r="O231" t="n">
         <v>20</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.04151262154415598</v>
       </c>
@@ -38549,9 +38351,6 @@
       <c r="O235" t="n">
         <v>3</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -39093,9 +38892,6 @@
       <c r="O238" t="n">
         <v>6</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.01245378646324679</v>
       </c>
@@ -39685,9 +39481,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -40229,9 +40022,6 @@
       <c r="O245" t="n">
         <v>4</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -40821,9 +40611,6 @@
       <c r="O249" t="n">
         <v>2</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -41365,9 +41152,6 @@
       <c r="O252" t="n">
         <v>4</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -41809,9 +41593,6 @@
       <c r="O255" t="n">
         <v>6</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.1129225349528181</v>
       </c>
@@ -42353,9 +42134,6 @@
       <c r="O258" t="n">
         <v>9</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.01861177153603757</v>
       </c>
@@ -42797,9 +42575,6 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -43341,9 +43116,6 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -43785,9 +43557,6 @@
       <c r="O267" t="n">
         <v>3</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.05646126747640907</v>
       </c>
@@ -44329,9 +44098,6 @@
       <c r="O270" t="n">
         <v>3</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -44773,9 +44539,6 @@
       <c r="O273" t="n">
         <v>3</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.05646126747640907</v>
       </c>
@@ -45317,9 +45080,6 @@
       <c r="O276" t="n">
         <v>3</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -45761,9 +45521,6 @@
       <c r="O279" t="n">
         <v>4</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.07528168996854542</v>
       </c>
@@ -46305,9 +46062,6 @@
       <c r="O282" t="n">
         <v>1</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -46749,9 +46503,6 @@
       <c r="O285" t="n">
         <v>5</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -47293,9 +47044,6 @@
       <c r="O288" t="n">
         <v>4</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -47737,9 +47485,6 @@
       <c r="O291" t="n">
         <v>3</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0.05646126747640907</v>
       </c>
@@ -48281,9 +48026,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -48725,9 +48467,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -49269,9 +49008,6 @@
       <c r="O300" t="n">
         <v>8</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0.01654379692092229</v>
       </c>
@@ -49713,9 +49449,6 @@
       <c r="O303" t="n">
         <v>2</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -50257,9 +49990,6 @@
       <c r="O306" t="n">
         <v>14</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="R306" t="n">
         <v>0.02895164461161399</v>
       </c>
@@ -50701,9 +50431,6 @@
       <c r="O309" t="n">
         <v>2</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -51245,9 +50972,6 @@
       <c r="O312" t="n">
         <v>5</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.01033987307557643</v>
       </c>
@@ -51689,9 +51413,6 @@
       <c r="O315" t="n">
         <v>4</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.07528168996854542</v>
       </c>
@@ -52233,9 +51954,6 @@
       <c r="O318" t="n">
         <v>2</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -52677,9 +52395,6 @@
       <c r="O321" t="n">
         <v>1</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -53221,9 +52936,6 @@
       <c r="O324" t="n">
         <v>1</v>
       </c>
-      <c r="Q324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -53813,9 +53525,6 @@
       <c r="O328" t="n">
         <v>6</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.1123836162294304</v>
       </c>
@@ -54357,9 +54066,6 @@
       <c r="O331" t="n">
         <v>5</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0.01029936409769182</v>
       </c>
@@ -54949,9 +54655,6 @@
       <c r="O335" t="n">
         <v>6</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0.1123836162294304</v>
       </c>
@@ -55493,9 +55196,6 @@
       <c r="O338" t="n">
         <v>8</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.01647898255630691</v>
       </c>
@@ -56085,9 +55785,6 @@
       <c r="O342" t="n">
         <v>5</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.09365301352452535</v>
       </c>
@@ -56629,9 +56326,6 @@
       <c r="O345" t="n">
         <v>4</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -57221,9 +56915,6 @@
       <c r="O349" t="n">
         <v>2</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -57765,9 +57456,6 @@
       <c r="O352" t="n">
         <v>2</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -58357,9 +58045,6 @@
       <c r="O356" t="n">
         <v>2</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -58901,9 +58586,6 @@
       <c r="O359" t="n">
         <v>2</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -59493,9 +59175,6 @@
       <c r="O363" t="n">
         <v>3</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.0561918081147152</v>
       </c>
@@ -60037,9 +59716,6 @@
       <c r="O366" t="n">
         <v>4</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -60629,9 +60305,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -61173,9 +60846,6 @@
       <c r="O373" t="n">
         <v>6</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.01235923691723018</v>
       </c>
@@ -61765,9 +61435,6 @@
       <c r="O377" t="n">
         <v>1</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -62309,9 +61976,6 @@
       <c r="O380" t="n">
         <v>11</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0.022658601014922</v>
       </c>
@@ -62901,9 +62565,6 @@
       <c r="O384" t="n">
         <v>1</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -63445,9 +63106,6 @@
       <c r="O387" t="n">
         <v>7</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0.01441910973676854</v>
       </c>
@@ -64037,9 +63695,6 @@
       <c r="O391" t="n">
         <v>2</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -64581,9 +64236,6 @@
       <c r="O394" t="n">
         <v>1</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -65173,9 +64825,6 @@
       <c r="O398" t="n">
         <v>3</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.0561918081147152</v>
       </c>
@@ -65717,9 +65366,6 @@
       <c r="O401" t="n">
         <v>6</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.01235923691723018</v>
       </c>
@@ -66309,9 +65955,6 @@
       <c r="O405" t="n">
         <v>4</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -66852,9 +66495,6 @@
       </c>
       <c r="O408" t="n">
         <v>3</v>
-      </c>
-      <c r="Q408" t="n">
-        <v>0</v>
       </c>
       <c r="R408" t="n">
         <v>0.00617961845861509</v>
